--- a/hlookup.xlsx
+++ b/hlookup.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\excel projects\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1F494C-9427-43CF-AA50-E6AAEDEFAA3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="90" windowWidth="19095" windowHeight="7170" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,15 +19,48 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="35">
   <si>
     <t>Regin</t>
   </si>
@@ -80,14 +119,59 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Sum of North</t>
+    <t>Sum of West</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>rahul</t>
+  </si>
+  <si>
+    <t>sonny</t>
+  </si>
+  <si>
+    <t>rames</t>
+  </si>
+  <si>
+    <t>mathur</t>
+  </si>
+  <si>
+    <t>mohan</t>
+  </si>
+  <si>
+    <t>ranchi</t>
+  </si>
+  <si>
+    <t>patna</t>
+  </si>
+  <si>
+    <t>tata</t>
+  </si>
+  <si>
+    <t>bokaro</t>
+  </si>
+  <si>
+    <t>danbad</t>
+  </si>
+  <si>
+    <t>HLOOKUP Used below</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hlookup used below</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,8 +202,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Agency FB"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Adobe Caslon Pro"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -162,8 +268,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -195,24 +331,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -221,24 +379,47 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -247,20 +428,66 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[hlookup.xlsx]Sheet4!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
-      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
@@ -275,82 +502,971 @@
         <c:idx val="3"/>
       </c:pivotFmt>
       <c:pivotFmt>
+        <c:idx val="4"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
         <c:idx val="5"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="17"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="6"/>
+        <c:idx val="18"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="7"/>
+        <c:idx val="19"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="8"/>
+        <c:idx val="20"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="9"/>
+        <c:idx val="21"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="10"/>
+        <c:idx val="22"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="11"/>
+        <c:idx val="23"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="12"/>
+        <c:idx val="24"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="13"/>
+        <c:idx val="25"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="14"/>
+        <c:idx val="26"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="15"/>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
+        <c:idx val="27"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="16"/>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
+        <c:idx val="28"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="17"/>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
+        <c:idx val="29"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="30"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="31"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="32"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -371,6 +1487,220 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-21D5-42C9-ABC4-E170EB78314F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-21D5-42C9-ABC4-E170EB78314F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-21D5-42C9-ABC4-E170EB78314F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-21D5-42C9-ABC4-E170EB78314F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-21D5-42C9-ABC4-E170EB78314F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-21D5-42C9-ABC4-E170EB78314F}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:sysClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Sheet4!$A$5:$A$11</c:f>
@@ -404,37 +1734,133 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>400</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>500</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>600</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>700</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>800</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>900</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2854-4ED9-9206-8A5CE8595D93}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
         <c:firstSliceAng val="0"/>
         <c:holeSize val="50"/>
       </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -443,24 +1869,671 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>409574</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>819150</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -479,7 +2552,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="DINESHWAR" refreshedDate="46283.042377546299" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="6">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="DINESHWAR" refreshedDate="46283.042377546299" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="6" xr:uid="{00000000-000A-0000-FFFF-FFFF04000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A4:E10" sheet="Sheet2"/>
   </cacheSource>
@@ -521,6 +2594,11 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20" maxValue="120"/>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
@@ -572,21 +2650,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A4:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
       <items count="7">
         <item x="0"/>
         <item x="1"/>
@@ -608,7 +2675,18 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -641,10 +2719,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of North" fld="1" baseField="0" baseItem="0"/>
+    <dataField name="Sum of West" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="15" series="1">
+  <chartFormats count="7">
+    <chartFormat chart="0" format="25" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -653,29 +2731,106 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="0" format="27">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="28">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="29">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="30">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="31">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="32">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E2" totalsRowShown="0">
-  <autoFilter ref="A1:E2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:E2" totalsRowShown="0">
+  <autoFilter ref="A1:E2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="Regin"/>
-    <tableColumn id="2" name="North"/>
-    <tableColumn id="3" name="South"/>
-    <tableColumn id="4" name="West"/>
-    <tableColumn id="5" name="East"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Regin"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="North"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="South"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="West"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="East"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -713,7 +2868,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -747,6 +2902,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -781,9 +2937,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -956,20 +3113,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="15" max="15" width="8.5703125" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -982,7 +3143,7 @@
       <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="16" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -991,195 +3152,435 @@
       <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="8" t="s">
         <v>13</v>
       </c>
+      <c r="N2" s="19" t="str" cm="1">
+        <f t="array" ref="N2:T6">TRANSPOSE(A2:E8)</f>
+        <v>Regin</v>
+      </c>
+      <c r="O2" s="21" t="str">
+        <v>1 Sales</v>
+      </c>
+      <c r="P2" s="21" t="str">
+        <v>2 Sales</v>
+      </c>
+      <c r="Q2" s="21" t="str">
+        <v>3 Sales</v>
+      </c>
+      <c r="R2" s="21" t="str">
+        <v>4 Sales</v>
+      </c>
+      <c r="S2" s="21" t="str">
+        <v>5 Sales</v>
+      </c>
+      <c r="T2" s="21" t="str">
+        <v>6 Sales</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="5">
         <v>400</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>100</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>50</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="10">
         <f>IFERROR(HLOOKUP(H2,A2:E9,8,0),"")</f>
         <v>1350</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="20">
         <f>HLOOKUP(K2,A2:E9,2,0)</f>
         <v>20</v>
       </c>
+      <c r="N3" s="19" t="str">
+        <v>North</v>
+      </c>
+      <c r="O3" s="21">
+        <v>400</v>
+      </c>
+      <c r="P3" s="21">
+        <v>500</v>
+      </c>
+      <c r="Q3" s="21">
+        <v>600</v>
+      </c>
+      <c r="R3" s="21">
+        <v>700</v>
+      </c>
+      <c r="S3" s="21">
+        <v>800</v>
+      </c>
+      <c r="T3" s="21">
+        <v>900</v>
+      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>500</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>150</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>100</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>40</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="20">
         <f t="shared" ref="K4:K8" si="0">HLOOKUP(K3,A3:E10,2,0)</f>
         <v>40</v>
       </c>
+      <c r="N4" s="19" t="str">
+        <v>South</v>
+      </c>
+      <c r="O4" s="21">
+        <v>100</v>
+      </c>
+      <c r="P4" s="21">
+        <v>150</v>
+      </c>
+      <c r="Q4" s="21">
+        <v>200</v>
+      </c>
+      <c r="R4" s="21">
+        <v>250</v>
+      </c>
+      <c r="S4" s="21">
+        <v>300</v>
+      </c>
+      <c r="T4" s="21">
+        <v>350</v>
+      </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>600</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>200</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>150</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>60</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="20">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
+      <c r="N5" s="19" t="str">
+        <v>West</v>
+      </c>
+      <c r="O5" s="21">
+        <v>50</v>
+      </c>
+      <c r="P5" s="21">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="21">
+        <v>150</v>
+      </c>
+      <c r="R5" s="21">
+        <v>200</v>
+      </c>
+      <c r="S5" s="21">
+        <v>250</v>
+      </c>
+      <c r="T5" s="21">
+        <v>300</v>
+      </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>700</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>250</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>200</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>80</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="20">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
+      <c r="N6" s="19" t="str">
+        <v>East</v>
+      </c>
+      <c r="O6" s="21">
+        <v>20</v>
+      </c>
+      <c r="P6" s="21">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="21">
+        <v>60</v>
+      </c>
+      <c r="R6" s="21">
+        <v>80</v>
+      </c>
+      <c r="S6" s="21">
+        <v>100</v>
+      </c>
+      <c r="T6" s="21">
+        <v>120</v>
+      </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>800</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>300</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>250</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>100</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="20">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>900</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>350</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>300</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>120</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="20">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
+      <c r="N8" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="8">
         <f>B3+B4+B5+B6+B7+B8</f>
         <v>3900</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="8">
         <f>C3+C4+C5+C6+C7+C8</f>
         <v>1350</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="8">
         <f>D3+D4+D5+D6+D7+D8</f>
         <v>1050</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="8">
         <f>E3+E4+E5+E6+E7+E8</f>
         <v>420</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="8">
         <f>HLOOKUP(K2,A2:E9,8,0)</f>
         <v>420</v>
       </c>
+      <c r="N9" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="25">
+        <f>HLOOKUP(N9,O2:T6,3,)</f>
+        <v>250</v>
+      </c>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+    </row>
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M10" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M11" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="N11" s="20">
+        <f>HLOOKUP($N$10,$O$2:$T$6,ROW(O2),0)</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="M12" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="N12" s="20">
+        <f t="shared" ref="N12:N14" si="1">HLOOKUP($N$10,$O$2:$T$6,ROW(O3),0)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="20">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="8">
+        <v>34</v>
+      </c>
+      <c r="C14" s="8">
+        <v>67</v>
+      </c>
+      <c r="D14" s="8">
+        <v>35</v>
+      </c>
+      <c r="E14" s="8">
+        <v>80</v>
+      </c>
+      <c r="F14" s="8">
+        <v>26</v>
+      </c>
+      <c r="M14" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="N14" s="20">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="24"/>
+    </row>
+    <row r="18" spans="1:4" ht="24.75" x14ac:dyDescent="0.7">
+      <c r="B18" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+    </row>
+    <row r="19" spans="1:4" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19">
+        <f>HLOOKUP(A19,A13:F15,2,0)</f>
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="N8:Q8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1187,11 +3588,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1208,7 +3609,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1234,80 +3635,79 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A4:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.140625" customWidth="1"/>
     <col min="6" max="7" width="4" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:2">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="21">
-        <v>400</v>
+      <c r="B5">
+        <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="21">
-        <v>500</v>
+      <c r="B6">
+        <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="21">
-        <v>600</v>
+      <c r="B7">
+        <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="21">
-        <v>700</v>
+      <c r="B8">
+        <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="21">
-        <v>800</v>
+      <c r="B9">
+        <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="20" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="21">
-        <v>900</v>
+      <c r="B10">
+        <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="21">
-        <v>3900</v>
+      <c r="B11">
+        <v>1050</v>
       </c>
     </row>
   </sheetData>
@@ -1317,26 +3717,26 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:I11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="1:9" ht="21">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
       <c r="H3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1355,127 +3755,127 @@
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="16"/>
+      <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="5">
         <v>400</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>100</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>50</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>500</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>150</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>100</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>600</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>200</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>150</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>700</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>250</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>200</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>800</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>300</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>250</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>900</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>350</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>300</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="8">
         <f>B5+B6+B7+B8+B9+B10</f>
         <v>3900</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="8">
         <f>C5+C6+C7+C8+C9+C10</f>
         <v>1350</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="8">
         <f>D5+D6+D7+D8+D9+D10</f>
         <v>1050</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="8">
         <f>E5+E6+E7+E8+E9+E10</f>
         <v>420</v>
       </c>
@@ -1489,9 +3889,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
